--- a/outputs/tables/script02_add_health_documentation_inventory.xlsx
+++ b/outputs/tables/script02_add_health_documentation_inventory.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="658">
   <si>
     <t xml:space="preserve">file_name</t>
   </si>
@@ -61,6 +61,81 @@
     <t xml:space="preserve">review_status</t>
   </si>
   <si>
+    <t xml:space="preserve">add_health_wave01_in_home_public_use_codebook_questionnaire.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/metadata/add_health_codebooks/add_health_wave01_in_home_public_use_codebook_questionnaire.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add_health_codebooks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">codebook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wave I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wave I baseline period, verify in documentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">public_use_documentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High: required for variable mapping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prefer not to commit PDF; cite official source and commit inventory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">priority_for_variable_mapping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add_health_wave01_in_home_public_use_variable_description_frequencies.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/metadata/add_health_codebooks/add_health_wave01_in_home_public_use_variable_description_frequencies.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unclassified_document</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To be reviewed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prefer not to commit PDF; commit inventory only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">needs_manual_review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add_health_wave02_in_home_public_use_codebook_questionnaire.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/metadata/add_health_codebooks/add_health_wave02_in_home_public_use_codebook_questionnaire.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wave II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wave II period, verify in documentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add_health_wave03_in_home_public_use_codebook_questionnaire.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/metadata/add_health_codebooks/add_health_wave03_in_home_public_use_codebook_questionnaire.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wave III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wave III period, verify in documentation</t>
+  </si>
+  <si>
     <t xml:space="preserve">add_health_1994_2018_icpsr21600_public_use_overview.pdf</t>
   </si>
   <si>
@@ -70,9 +145,6 @@
     <t xml:space="preserve">add_health_icpsr</t>
   </si>
   <si>
-    <t xml:space="preserve">pdf</t>
-  </si>
-  <si>
     <t xml:space="preserve">icpsr_public_use_overview</t>
   </si>
   <si>
@@ -82,15 +154,9 @@
     <t xml:space="preserve">1994-2018</t>
   </si>
   <si>
-    <t xml:space="preserve">public_use_documentation</t>
-  </si>
-  <si>
     <t xml:space="preserve">High: identifies public-use study and documentation source</t>
   </si>
   <si>
-    <t xml:space="preserve">Prefer not to commit PDF; commit inventory only.</t>
-  </si>
-  <si>
     <t xml:space="preserve">reviewed_for_public_use_overview</t>
   </si>
   <si>
@@ -142,9 +208,6 @@
     <t xml:space="preserve">survey_mode_transition_report</t>
   </si>
   <si>
-    <t xml:space="preserve">To be reviewed</t>
-  </si>
-  <si>
     <t xml:space="preserve">add_health_social_behavioral_genetic_linkages.pdf</t>
   </si>
   <si>
@@ -202,9 +265,6 @@
     <t xml:space="preserve">High: required for data structure and analytical decisions</t>
   </si>
   <si>
-    <t xml:space="preserve">Prefer not to commit PDF; cite official source and commit inventory.</t>
-  </si>
-  <si>
     <t xml:space="preserve">reviewed_for_design_and_weights</t>
   </si>
   <si>
@@ -259,6 +319,12 @@
     <t xml:space="preserve">Do not commit PDF; keep local. Use only to document restrictions.</t>
   </si>
   <si>
+    <t xml:space="preserve">add_health_waves01_03_04_longitudinal_weight_user_guide.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/metadata/add_health_user_guides/add_health_waves01_03_04_longitudinal_weight_user_guide.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">add_health_waves01_06_sample_sizes_composition_weights_guide.pdf</t>
   </si>
   <si>
@@ -343,15 +409,15 @@
     <t xml:space="preserve">Public-use codebooks for variable mapping</t>
   </si>
   <si>
+    <t xml:space="preserve">data/metadata/add_health_questionnaires</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Questionnaires for question wording and construct mapping</t>
+  </si>
+  <si>
     <t xml:space="preserve">empty_pending</t>
   </si>
   <si>
-    <t xml:space="preserve">data/metadata/add_health_questionnaires</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Questionnaires for question wording and construct mapping</t>
-  </si>
-  <si>
     <t xml:space="preserve">data/metadata/add_health_user_guides</t>
   </si>
   <si>
@@ -406,16 +472,13 @@
     <t xml:space="preserve">grade school grade current grade</t>
   </si>
   <si>
-    <t xml:space="preserve">Wave I</t>
-  </si>
-  <si>
     <t xml:space="preserve">High</t>
   </si>
   <si>
-    <t xml:space="preserve">ICPSR Variables and Add Health Codebook Explorer; local codebooks still pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codebooks_and_questionnaires_pending</t>
+    <t xml:space="preserve">Local codebooks, ICPSR Variables and Add Health Codebook Explorer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">codebooks_available_questionnaires_pending</t>
   </si>
   <si>
     <t xml:space="preserve">to_be_verified</t>
@@ -724,7 +787,7 @@
     <t xml:space="preserve">Direct district equivalence is not expected in Add Health.</t>
   </si>
   <si>
-    <t xml:space="preserve">local_codebooks_and_questionnaires_pending</t>
+    <t xml:space="preserve">ready_for_codebook_review_questionnaires_pending</t>
   </si>
   <si>
     <t xml:space="preserve">Search ICPSR Variables and Add Health Codebook Explorer using Script 01b keywords</t>
@@ -2267,8 +2330,8 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="64.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="101.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="73.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="108.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="22.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
@@ -2359,10 +2422,10 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>585.8</v>
+        <v>2878.5</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46205.5934027778</v>
+        <v>43918.8974305556</v>
       </c>
       <c r="G2" t="s">
         <v>17</v>
@@ -2394,224 +2457,224 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>688.7</v>
+        <v>63497</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>46205.5015277778</v>
+        <v>43918.8976388889</v>
       </c>
       <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
         <v>27</v>
       </c>
-      <c r="H3" t="s">
+      <c r="L3" t="s">
         <v>28</v>
       </c>
-      <c r="I3" t="s">
+      <c r="M3" t="s">
         <v>29</v>
-      </c>
-      <c r="J3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>693.6</v>
+        <v>2197</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46205.5027314815</v>
+        <v>43916.1170601852</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K4" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>598.9</v>
+        <v>3238.5</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46205.5014814815</v>
+        <v>44005.2541898148</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="J5" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L5" t="s">
         <v>22</v>
       </c>
       <c r="M5" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>639.7</v>
+        <v>585.8</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46205.5025694444</v>
+        <v>46205.5934027778</v>
       </c>
       <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" t="s">
         <v>43</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6" t="s">
         <v>28</v>
       </c>
-      <c r="I6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" t="s">
-        <v>22</v>
-      </c>
       <c r="M6" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>579</v>
+        <v>688.7</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>46205.5018055556</v>
+        <v>46205.5015277778</v>
       </c>
       <c r="G7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J7" t="s">
+        <v>52</v>
+      </c>
+      <c r="K7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" t="s">
         <v>28</v>
       </c>
-      <c r="I7" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L7" t="s">
-        <v>22</v>
-      </c>
       <c r="M7" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" t="s">
         <v>48</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>223</v>
+        <v>693.6</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46205.5032638889</v>
+        <v>46205.5027314815</v>
       </c>
       <c r="G8" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H8" t="s">
         <v>50</v>
@@ -2620,57 +2683,57 @@
         <v>51</v>
       </c>
       <c r="J8" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="K8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="L8" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M8" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>991.1</v>
+        <v>598.9</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>43914.8271527778</v>
+        <v>46205.5014814815</v>
       </c>
       <c r="G9" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="I9" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J9" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="K9" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="L9" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="M9" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -2681,37 +2744,37 @@
         <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>436</v>
+        <v>639.7</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>43914.8271527778</v>
+        <v>46205.5025694444</v>
       </c>
       <c r="G10" t="s">
         <v>64</v>
       </c>
       <c r="H10" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="I10" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J10" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="K10" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="L10" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="M10" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -2722,242 +2785,447 @@
         <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
         <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>953.6</v>
+        <v>579</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>46205.5031018519</v>
+        <v>46205.5018055556</v>
       </c>
       <c r="G11" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H11" t="s">
+        <v>50</v>
+      </c>
+      <c r="I11" t="s">
+        <v>51</v>
+      </c>
+      <c r="J11" t="s">
+        <v>52</v>
+      </c>
+      <c r="K11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L11" t="s">
         <v>28</v>
       </c>
-      <c r="I11" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" t="s">
-        <v>30</v>
-      </c>
-      <c r="K11" t="s">
-        <v>59</v>
-      </c>
-      <c r="L11" t="s">
-        <v>60</v>
-      </c>
       <c r="M11" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
         <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>470.4</v>
+        <v>223</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>46205.5035185185</v>
+        <v>46205.5032638889</v>
       </c>
       <c r="G12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J12" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="K12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M12" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
       </c>
       <c r="E13" t="n">
-        <v>925.4</v>
+        <v>991.1</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>46205.5028703704</v>
+        <v>43914.8271527778</v>
       </c>
       <c r="G13" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="H13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I13" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J13" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="K13" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="L13" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="M13" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
         <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>545.2</v>
+        <v>436</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>46205.5006944444</v>
+        <v>43914.8271527778</v>
       </c>
       <c r="G14" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J14" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K14" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L14" t="s">
         <v>22</v>
       </c>
       <c r="M14" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
         <v>16</v>
       </c>
       <c r="E15" t="n">
-        <v>681.2</v>
+        <v>953.6</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>46205.4590972222</v>
+        <v>46205.5031018519</v>
       </c>
       <c r="G15" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H15" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="I15" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="J15" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="K15" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="L15" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="M15" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
         <v>16</v>
       </c>
       <c r="E16" t="n">
+        <v>470.4</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>46205.5035185185</v>
+      </c>
+      <c r="G16" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" t="s">
+        <v>90</v>
+      </c>
+      <c r="I16" t="s">
+        <v>91</v>
+      </c>
+      <c r="J16" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16" t="s">
+        <v>92</v>
+      </c>
+      <c r="L16" t="s">
+        <v>28</v>
+      </c>
+      <c r="M16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" t="n">
+        <v>925.4</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>46205.5028703704</v>
+      </c>
+      <c r="G17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" t="s">
+        <v>95</v>
+      </c>
+      <c r="I17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J17" t="s">
+        <v>97</v>
+      </c>
+      <c r="K17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L17" t="s">
+        <v>98</v>
+      </c>
+      <c r="M17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" t="n">
+        <v>433.5</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>43918.8975925926</v>
+      </c>
+      <c r="G18" t="s">
+        <v>89</v>
+      </c>
+      <c r="H18" t="s">
+        <v>50</v>
+      </c>
+      <c r="I18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J18" t="s">
+        <v>52</v>
+      </c>
+      <c r="K18" t="s">
+        <v>92</v>
+      </c>
+      <c r="L18" t="s">
+        <v>28</v>
+      </c>
+      <c r="M18" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" t="n">
+        <v>545.2</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>46205.5006944444</v>
+      </c>
+      <c r="G19" t="s">
+        <v>89</v>
+      </c>
+      <c r="H19" t="s">
+        <v>103</v>
+      </c>
+      <c r="I19" t="s">
+        <v>96</v>
+      </c>
+      <c r="J19" t="s">
+        <v>52</v>
+      </c>
+      <c r="K19" t="s">
+        <v>92</v>
+      </c>
+      <c r="L19" t="s">
+        <v>28</v>
+      </c>
+      <c r="M19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" t="n">
+        <v>681.2</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>46205.4590972222</v>
+      </c>
+      <c r="G20" t="s">
+        <v>107</v>
+      </c>
+      <c r="H20" t="s">
+        <v>50</v>
+      </c>
+      <c r="I20" t="s">
+        <v>51</v>
+      </c>
+      <c r="J20" t="s">
+        <v>108</v>
+      </c>
+      <c r="K20" t="s">
+        <v>109</v>
+      </c>
+      <c r="L20" t="s">
+        <v>110</v>
+      </c>
+      <c r="M20" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" t="n">
         <v>229</v>
       </c>
-      <c r="F16" s="1" t="n">
+      <c r="F21" s="1" t="n">
         <v>46205.4719212963</v>
       </c>
-      <c r="G16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H16" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" t="s">
-        <v>29</v>
-      </c>
-      <c r="J16" t="s">
-        <v>86</v>
-      </c>
-      <c r="K16" t="s">
-        <v>87</v>
-      </c>
-      <c r="L16" t="s">
-        <v>88</v>
-      </c>
-      <c r="M16" t="s">
-        <v>89</v>
+      <c r="G21" t="s">
+        <v>114</v>
+      </c>
+      <c r="H21" t="s">
+        <v>50</v>
+      </c>
+      <c r="I21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J21" t="s">
+        <v>108</v>
+      </c>
+      <c r="K21" t="s">
+        <v>109</v>
+      </c>
+      <c r="L21" t="s">
+        <v>110</v>
+      </c>
+      <c r="M21" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -3022,7 +3290,7 @@
         <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2">
@@ -3039,21 +3307,21 @@
         <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
         <v>26</v>
       </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3061,16 +3329,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -3078,16 +3346,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
         <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3095,16 +3363,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -3112,16 +3380,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -3129,16 +3397,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -3146,16 +3414,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -3163,16 +3431,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -3180,16 +3448,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -3197,16 +3465,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -3214,33 +3482,33 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" t="s">
         <v>84</v>
       </c>
-      <c r="B14" t="s">
-        <v>85</v>
-      </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -3248,18 +3516,52 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3319,37 +3621,37 @@
         <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -3357,10 +3659,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -3368,21 +3670,21 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -3390,12 +3692,45 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3452,28 +3787,28 @@
         <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="B4" t="n">
         <v>2</v>
@@ -3481,7 +3816,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
@@ -3537,27 +3872,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="B1" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="C1" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="D1" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="E1" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
@@ -3566,15 +3901,15 @@
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
@@ -3583,15 +3918,15 @@
         <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
@@ -3600,32 +3935,32 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
@@ -3634,24 +3969,24 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -3670,8 +4005,8 @@
     <col min="3" max="3" width="69.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="51.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="15.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="79.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="36.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="65.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="42.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="23.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="24.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="14.71" hidden="0" customWidth="1"/>
@@ -3704,918 +4039,918 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="B1" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="C1" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="D1" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="E1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="F1" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="G1" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="H1" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="I1" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="J1" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="K1" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="L1" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="M1" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F2" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G2" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2"/>
       <c r="K2" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L2" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M2" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F3" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G3" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3"/>
       <c r="K3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="C4" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F4" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G4" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L4" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M4" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F5" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G5" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5"/>
       <c r="K5" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L5" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M5" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="E6" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F6" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G6" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
       <c r="J6"/>
       <c r="K6" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L6" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M6" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="B7" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="E7" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F7" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G7" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
       <c r="J7"/>
       <c r="K7" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L7" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M7" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="B8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" t="s">
+        <v>166</v>
+      </c>
+      <c r="E8" t="s">
         <v>150</v>
       </c>
-      <c r="C8" t="s">
+      <c r="F8" t="s">
         <v>151</v>
       </c>
-      <c r="D8" t="s">
-        <v>145</v>
-      </c>
-      <c r="E8" t="s">
-        <v>129</v>
-      </c>
-      <c r="F8" t="s">
-        <v>130</v>
-      </c>
       <c r="G8" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H8"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L8" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M8" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G9" t="s">
         <v>152</v>
-      </c>
-      <c r="B9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C9" t="s">
-        <v>154</v>
-      </c>
-      <c r="D9" t="s">
-        <v>145</v>
-      </c>
-      <c r="E9" t="s">
-        <v>129</v>
-      </c>
-      <c r="F9" t="s">
-        <v>130</v>
-      </c>
-      <c r="G9" t="s">
-        <v>131</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L9" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M9" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="B10" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="E10" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F10" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G10" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L10" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M10" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="B11" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="C11" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="D11" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="E11" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F11" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G11" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="B12" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="C12" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="E12" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F12" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G12" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>187</v>
+      </c>
+      <c r="B13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13" t="s">
         <v>166</v>
       </c>
-      <c r="B13" t="s">
-        <v>167</v>
-      </c>
-      <c r="C13" t="s">
-        <v>168</v>
-      </c>
-      <c r="D13" t="s">
-        <v>145</v>
-      </c>
       <c r="E13" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="F13" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G13" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L13" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M13" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="B14" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="D14" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="E14" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="F14" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G14" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L14" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M14" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="B15" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="C15" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="E15" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="F15" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G15" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L15" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M15" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="B16" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="C16" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="E16" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F16" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G16" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L16" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M16" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="C17" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="D17" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="E17" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F17" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G17" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L17" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M17" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="B18" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="C18" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="E18" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F18" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G18" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L18" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M18" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="C19" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="D19" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="E19" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F19" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G19" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L19" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M19" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="C20" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="E20" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F20" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G20" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L20" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M20" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="C21" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="D21" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="E21" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F21" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G21" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L21" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M21" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="C22" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="D22" t="s">
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="E22" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F22" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G22" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L22" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M22" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="C23" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="D23" t="s">
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="E23" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F23" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G23" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H23"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L23" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M23" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="B24" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="C24" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="D24" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E24" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F24" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G24" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H24"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L24" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M24" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="C25" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="D25" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E25" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="F25" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G25" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L25" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M25" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="B26" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="C26" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="D26" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="E26" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F26" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G26" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L26" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M26" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -4644,7 +4979,7 @@
     <col min="13" max="13" width="17.71" hidden="0" customWidth="1"/>
     <col min="14" max="14" width="15.71" hidden="0" customWidth="1"/>
     <col min="15" max="15" width="59.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="42.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="48.71" hidden="0" customWidth="1"/>
     <col min="17" max="17" width="81.71" hidden="0" customWidth="1"/>
     <col min="18" max="18" width="9.15" hidden="0" customWidth="1"/>
     <col min="19" max="19" width="9.15" hidden="0" customWidth="1"/>
@@ -4668,3700 +5003,3700 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="B1" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="C1" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="D1" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="E1" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="F1" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="G1" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="H1" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="I1" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="J1" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="K1" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="L1" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="M1" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="N1" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="O1" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="P1" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="Q1" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C2" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="D2" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E2" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="F2" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="G2" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="H2" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
       <c r="K2"/>
       <c r="L2"/>
       <c r="M2" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N2" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O2" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="P2" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q2" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="B3" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="C3" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="D3" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E3" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="F3" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="G3" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="H3" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="I3"/>
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3"/>
       <c r="M3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O3" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="P3" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q3" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="C4" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E4" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="F4" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="G4" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="H4" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4"/>
       <c r="M4" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N4" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O4" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="P4" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q4" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="B5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D5" t="s">
         <v>249</v>
       </c>
-      <c r="C5" t="s">
-        <v>250</v>
-      </c>
-      <c r="D5" t="s">
-        <v>228</v>
-      </c>
       <c r="E5" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="F5" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="G5" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="H5" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5"/>
       <c r="M5" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N5" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O5" t="s">
+        <v>276</v>
+      </c>
+      <c r="P5" t="s">
         <v>255</v>
       </c>
-      <c r="P5" t="s">
-        <v>234</v>
-      </c>
       <c r="Q5" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="B6" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C6" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="D6" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E6" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="F6" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="G6" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="H6" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6"/>
       <c r="M6" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N6" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O6" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="P6" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q6" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="B7" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="C7" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="D7" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E7" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="F7" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="G7" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="H7" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
       <c r="K7"/>
       <c r="L7"/>
       <c r="M7" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N7" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O7" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="P7" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q7" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="B8" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="C8" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="D8" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E8" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="F8" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="G8" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="H8" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
       <c r="L8"/>
       <c r="M8" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N8" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O8" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="P8" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q8" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="B9" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="C9" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="D9" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E9" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="F9" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="G9" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="H9" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
       <c r="L9"/>
       <c r="M9" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N9" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O9" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="P9" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q9" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="B10" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="C10" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="D10" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E10" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="F10" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="G10" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="H10" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
       <c r="L10"/>
       <c r="M10" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N10" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O10" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="P10" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q10" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="B11" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="C11" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="D11" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="E11" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="F11" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="G11" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="H11" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11"/>
       <c r="M11" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N11" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O11" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="P11" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q11" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="B12" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="C12" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="D12" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="E12" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="F12" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="G12" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="H12" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12"/>
       <c r="M12" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N12" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O12" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="P12" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q12" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="B13" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="C13" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="D13" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="E13" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="F13" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="G13" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="H13" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
       <c r="L13"/>
       <c r="M13" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N13" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O13" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="P13" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q13" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="B14" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="C14" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="D14" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="E14" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="F14" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="G14" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="H14" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14"/>
       <c r="M14" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N14" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O14" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="P14" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q14" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="B15" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="C15" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="D15" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="E15" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="F15" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="G15" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="H15" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
       <c r="L15"/>
       <c r="M15" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N15" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O15" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="P15" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q15" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B16" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="C16" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="D16" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E16" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="F16" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G16" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H16" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
       <c r="L16"/>
       <c r="M16" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N16" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O16" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="P16" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q16" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B17" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="C17" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="D17" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E17" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="F17" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G17" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H17" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
       <c r="L17"/>
       <c r="M17" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N17" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O17" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="P17" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q17" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B18" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="C18" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="D18" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E18" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="F18" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G18" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H18" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
       <c r="L18"/>
       <c r="M18" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N18" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O18" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="P18" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q18" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B19" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="C19" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="D19" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E19" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="F19" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G19" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H19" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
       <c r="L19"/>
       <c r="M19" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N19" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O19" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="P19" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q19" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B20" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="C20" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="D20" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E20" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="F20" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G20" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H20" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20"/>
       <c r="M20" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N20" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O20" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="P20" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q20" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B21" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="C21" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="D21" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E21" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="F21" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G21" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H21" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
       <c r="L21"/>
       <c r="M21" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N21" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O21" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="P21" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q21" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B22" t="s">
+        <v>360</v>
+      </c>
+      <c r="C22" t="s">
+        <v>361</v>
+      </c>
+      <c r="D22" t="s">
+        <v>338</v>
+      </c>
+      <c r="E22" t="s">
+        <v>191</v>
+      </c>
+      <c r="F22" t="s">
         <v>339</v>
       </c>
-      <c r="C22" t="s">
+      <c r="G22" t="s">
         <v>340</v>
       </c>
-      <c r="D22" t="s">
-        <v>317</v>
-      </c>
-      <c r="E22" t="s">
-        <v>170</v>
-      </c>
-      <c r="F22" t="s">
-        <v>318</v>
-      </c>
-      <c r="G22" t="s">
-        <v>319</v>
-      </c>
       <c r="H22" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22"/>
       <c r="M22" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N22" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O22" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="P22" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q22" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B23" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="C23" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="D23" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E23" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="F23" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G23" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H23" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23"/>
       <c r="M23" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N23" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O23" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="P23" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q23" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B24" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="C24" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="D24" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E24" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="F24" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G24" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H24" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
       <c r="L24"/>
       <c r="M24" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N24" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O24" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="P24" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q24" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B25" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="C25" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="D25" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E25" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="F25" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G25" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H25" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
       <c r="L25"/>
       <c r="M25" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N25" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O25" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="P25" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q25" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B26" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="C26" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="D26" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E26" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="F26" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G26" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H26" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
       <c r="L26"/>
       <c r="M26" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N26" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O26" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="P26" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q26" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B27" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="C27" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="D27" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E27" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="F27" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G27" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H27" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
       <c r="L27"/>
       <c r="M27" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N27" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O27" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="P27" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q27" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B28" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="C28" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="D28" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E28" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="F28" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G28" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H28" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
       <c r="L28"/>
       <c r="M28" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N28" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O28" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="P28" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q28" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B29" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="C29" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="D29" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E29" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="F29" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G29" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H29" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
       <c r="L29"/>
       <c r="M29" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N29" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O29" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="P29" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q29" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B30" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="C30" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="D30" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E30" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="F30" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G30" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H30" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
       <c r="L30"/>
       <c r="M30" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N30" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O30" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="P30" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q30" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B31" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="C31" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="D31" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="E31" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="F31" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G31" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="H31" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
       <c r="L31"/>
       <c r="M31" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N31" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O31" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="P31" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q31" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B32" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="C32" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="D32" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="E32" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="F32" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G32" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="H32" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
       <c r="L32"/>
       <c r="M32" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N32" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O32" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="P32" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q32" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B33" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="C33" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="D33" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="E33" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="F33" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G33" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="H33" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
       <c r="L33"/>
       <c r="M33" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N33" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="P33" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q33" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B34" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="C34" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="D34" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="E34" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="F34" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G34" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="H34" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
       <c r="L34"/>
       <c r="M34" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N34" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O34" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="P34" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q34" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B35" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="C35" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="D35" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="E35" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="F35" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G35" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="H35" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="I35"/>
       <c r="J35"/>
       <c r="K35"/>
       <c r="L35"/>
       <c r="M35" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N35" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O35" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="P35" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q35" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B36" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="C36" t="s">
+        <v>414</v>
+      </c>
+      <c r="D36" t="s">
         <v>393</v>
       </c>
-      <c r="D36" t="s">
-        <v>372</v>
-      </c>
       <c r="E36" t="s">
+        <v>415</v>
+      </c>
+      <c r="F36" t="s">
+        <v>339</v>
+      </c>
+      <c r="G36" t="s">
         <v>394</v>
       </c>
-      <c r="F36" t="s">
-        <v>318</v>
-      </c>
-      <c r="G36" t="s">
-        <v>373</v>
-      </c>
       <c r="H36" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="I36"/>
       <c r="J36"/>
       <c r="K36"/>
       <c r="L36"/>
       <c r="M36" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N36" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O36" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="P36" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q36" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B37" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="C37" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="D37" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="E37" t="s">
+        <v>415</v>
+      </c>
+      <c r="F37" t="s">
+        <v>339</v>
+      </c>
+      <c r="G37" t="s">
         <v>394</v>
       </c>
-      <c r="F37" t="s">
-        <v>318</v>
-      </c>
-      <c r="G37" t="s">
-        <v>373</v>
-      </c>
       <c r="H37" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="I37"/>
       <c r="J37"/>
       <c r="K37"/>
       <c r="L37"/>
       <c r="M37" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N37" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O37" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="P37" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q37" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="B38" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="C38" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="D38" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E38" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="F38" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="G38" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="H38" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="I38"/>
       <c r="J38"/>
       <c r="K38"/>
       <c r="L38"/>
       <c r="M38" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N38" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O38" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="P38" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q38" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="B39" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="C39" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="D39" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="E39" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="F39" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="G39" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="H39" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="I39"/>
       <c r="J39"/>
       <c r="K39"/>
       <c r="L39"/>
       <c r="M39" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N39" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O39" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="P39" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q39" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="B40" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="C40" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="D40" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E40" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="F40" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="G40" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="H40" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="I40"/>
       <c r="J40"/>
       <c r="K40"/>
       <c r="L40"/>
       <c r="M40" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N40" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O40" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="P40" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q40" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="B41" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="C41" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="D41" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E41" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="F41" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="G41" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="H41" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="I41"/>
       <c r="J41"/>
       <c r="K41"/>
       <c r="L41"/>
       <c r="M41" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N41" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O41" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="P41" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q41" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="B42" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="C42" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="D42" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E42" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="F42" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="G42" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="H42" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="I42"/>
       <c r="J42"/>
       <c r="K42"/>
       <c r="L42"/>
       <c r="M42" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N42" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O42" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="P42" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q42" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="B43" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="C43" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="D43" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E43" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="F43" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="G43" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="H43" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="I43"/>
       <c r="J43"/>
       <c r="K43"/>
       <c r="L43"/>
       <c r="M43" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N43" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O43" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="P43" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q43" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="B44" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="C44" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="D44" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E44" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="F44" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="G44" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="H44" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="I44"/>
       <c r="J44"/>
       <c r="K44"/>
       <c r="L44"/>
       <c r="M44" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N44" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O44" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="P44" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q44" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="B45" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="C45" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="D45" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E45" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="F45" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="G45" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="H45" t="s">
-        <v>445</v>
+        <v>466</v>
       </c>
       <c r="I45"/>
       <c r="J45"/>
       <c r="K45"/>
       <c r="L45"/>
       <c r="M45" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N45" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O45" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="P45" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q45" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="B46" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="C46" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="D46" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E46" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="F46" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="G46" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="H46" t="s">
-        <v>445</v>
+        <v>466</v>
       </c>
       <c r="I46"/>
       <c r="J46"/>
       <c r="K46"/>
       <c r="L46"/>
       <c r="M46" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N46" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O46" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="P46" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q46" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="B47" t="s">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="C47" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="D47" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E47" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="F47" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="G47" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="H47" t="s">
-        <v>445</v>
+        <v>466</v>
       </c>
       <c r="I47"/>
       <c r="J47"/>
       <c r="K47"/>
       <c r="L47"/>
       <c r="M47" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N47" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O47" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="P47" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q47" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="B48" t="s">
-        <v>451</v>
+        <v>472</v>
       </c>
       <c r="C48" t="s">
+        <v>473</v>
+      </c>
+      <c r="D48" t="s">
+        <v>393</v>
+      </c>
+      <c r="E48" t="s">
+        <v>474</v>
+      </c>
+      <c r="F48" t="s">
+        <v>475</v>
+      </c>
+      <c r="G48" t="s">
         <v>452</v>
       </c>
-      <c r="D48" t="s">
-        <v>372</v>
-      </c>
-      <c r="E48" t="s">
-        <v>453</v>
-      </c>
-      <c r="F48" t="s">
-        <v>454</v>
-      </c>
-      <c r="G48" t="s">
-        <v>431</v>
-      </c>
       <c r="H48" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="I48"/>
       <c r="J48"/>
       <c r="K48"/>
       <c r="L48"/>
       <c r="M48" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N48" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O48" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="P48" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q48" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="B49" t="s">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="C49" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E49" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="F49" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="G49" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="H49" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="I49"/>
       <c r="J49"/>
       <c r="K49"/>
       <c r="L49"/>
       <c r="M49" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N49" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O49" t="s">
-        <v>460</v>
+        <v>481</v>
       </c>
       <c r="P49" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q49" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="B50" t="s">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="C50" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="D50" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E50" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="F50" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="G50" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="H50" t="s">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="I50"/>
       <c r="J50"/>
       <c r="K50"/>
       <c r="L50"/>
       <c r="M50" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N50" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O50" t="s">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="P50" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q50" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B51" t="s">
-        <v>466</v>
+        <v>487</v>
       </c>
       <c r="C51" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
       <c r="D51" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E51" t="s">
-        <v>469</v>
+        <v>490</v>
       </c>
       <c r="F51" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G51" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H51" t="s">
-        <v>470</v>
+        <v>491</v>
       </c>
       <c r="I51"/>
       <c r="J51"/>
       <c r="K51"/>
       <c r="L51"/>
       <c r="M51" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N51" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O51" t="s">
-        <v>471</v>
+        <v>492</v>
       </c>
       <c r="P51" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q51" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B52" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="C52" t="s">
-        <v>473</v>
+        <v>494</v>
       </c>
       <c r="D52" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E52" t="s">
-        <v>474</v>
+        <v>495</v>
       </c>
       <c r="F52" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G52" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H52" t="s">
-        <v>475</v>
+        <v>496</v>
       </c>
       <c r="I52"/>
       <c r="J52"/>
       <c r="K52"/>
       <c r="L52"/>
       <c r="M52" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N52" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O52" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="P52" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q52" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B53" t="s">
-        <v>476</v>
+        <v>497</v>
       </c>
       <c r="C53" t="s">
-        <v>477</v>
+        <v>498</v>
       </c>
       <c r="D53" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E53" t="s">
-        <v>474</v>
+        <v>495</v>
       </c>
       <c r="F53" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G53" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H53" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="I53"/>
       <c r="J53"/>
       <c r="K53"/>
       <c r="L53"/>
       <c r="M53" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N53" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O53" t="s">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="P53" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q53" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B54" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="C54" t="s">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="D54" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E54" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="F54" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G54" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H54" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="I54"/>
       <c r="J54"/>
       <c r="K54"/>
       <c r="L54"/>
       <c r="M54" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N54" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O54" t="s">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="P54" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q54" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B55" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="C55" t="s">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="D55" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E55" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="F55" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G55" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H55" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="I55"/>
       <c r="J55"/>
       <c r="K55"/>
       <c r="L55"/>
       <c r="M55" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N55" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O55" t="s">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="P55" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q55" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B56" t="s">
-        <v>488</v>
+        <v>509</v>
       </c>
       <c r="C56" t="s">
+        <v>510</v>
+      </c>
+      <c r="D56" t="s">
         <v>489</v>
       </c>
-      <c r="D56" t="s">
-        <v>468</v>
-      </c>
       <c r="E56" t="s">
-        <v>490</v>
+        <v>511</v>
       </c>
       <c r="F56" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G56" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H56" t="s">
-        <v>491</v>
+        <v>512</v>
       </c>
       <c r="I56"/>
       <c r="J56"/>
       <c r="K56"/>
       <c r="L56"/>
       <c r="M56" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N56" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O56" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
       <c r="P56" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q56" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B57" t="s">
-        <v>493</v>
+        <v>514</v>
       </c>
       <c r="C57" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="D57" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E57" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="F57" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G57" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H57" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="I57"/>
       <c r="J57"/>
       <c r="K57"/>
       <c r="L57"/>
       <c r="M57" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N57" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O57" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="P57" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q57" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B58" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="C58" t="s">
-        <v>499</v>
+        <v>520</v>
       </c>
       <c r="D58" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E58" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="F58" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G58" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H58" t="s">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="I58"/>
       <c r="J58"/>
       <c r="K58"/>
       <c r="L58"/>
       <c r="M58" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N58" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O58" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="P58" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q58" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B59" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
       <c r="C59" t="s">
-        <v>502</v>
+        <v>523</v>
       </c>
       <c r="D59" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E59" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="F59" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G59" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H59" t="s">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c r="I59"/>
       <c r="J59"/>
       <c r="K59"/>
       <c r="L59"/>
       <c r="M59" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N59" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O59" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="P59" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q59" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B60" t="s">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="C60" t="s">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="D60" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E60" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="F60" t="s">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="G60" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H60" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="I60"/>
       <c r="J60"/>
       <c r="K60"/>
       <c r="L60"/>
       <c r="M60" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N60" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O60" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="P60" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q60" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B61" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
       <c r="C61" t="s">
-        <v>510</v>
+        <v>531</v>
       </c>
       <c r="D61" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E61" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="F61" t="s">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="G61" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H61" t="s">
-        <v>511</v>
+        <v>532</v>
       </c>
       <c r="I61"/>
       <c r="J61"/>
       <c r="K61"/>
       <c r="L61"/>
       <c r="M61" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N61" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O61" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="P61" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q61" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B62" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="C62" t="s">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="D62" t="s">
-        <v>514</v>
+        <v>535</v>
       </c>
       <c r="E62" t="s">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="F62" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="G62" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H62" t="s">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="I62"/>
       <c r="J62"/>
       <c r="K62"/>
       <c r="L62"/>
       <c r="M62" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N62" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O62" t="s">
-        <v>518</v>
+        <v>539</v>
       </c>
       <c r="P62" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q62" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B63" t="s">
-        <v>519</v>
+        <v>540</v>
       </c>
       <c r="C63" t="s">
-        <v>520</v>
+        <v>541</v>
       </c>
       <c r="D63" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E63" t="s">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="F63" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G63" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H63" t="s">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="I63"/>
       <c r="J63"/>
       <c r="K63"/>
       <c r="L63"/>
       <c r="M63" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N63" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O63" t="s">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="P63" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q63" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B64" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="C64" t="s">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="D64" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E64" t="s">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="F64" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G64" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H64" t="s">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="I64"/>
       <c r="J64"/>
       <c r="K64"/>
       <c r="L64"/>
       <c r="M64" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N64" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O64" t="s">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="P64" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q64" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B65" t="s">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="C65" t="s">
-        <v>528</v>
+        <v>549</v>
       </c>
       <c r="D65" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E65" t="s">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="F65" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G65" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H65" t="s">
-        <v>530</v>
+        <v>551</v>
       </c>
       <c r="I65"/>
       <c r="J65"/>
       <c r="K65"/>
       <c r="L65"/>
       <c r="M65" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N65" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O65" t="s">
-        <v>531</v>
+        <v>552</v>
       </c>
       <c r="P65" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q65" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B66" t="s">
-        <v>532</v>
+        <v>553</v>
       </c>
       <c r="C66" t="s">
-        <v>533</v>
+        <v>554</v>
       </c>
       <c r="D66" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E66" t="s">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="F66" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G66" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H66" t="s">
-        <v>534</v>
+        <v>555</v>
       </c>
       <c r="I66"/>
       <c r="J66"/>
       <c r="K66"/>
       <c r="L66"/>
       <c r="M66" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N66" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O66" t="s">
-        <v>535</v>
+        <v>556</v>
       </c>
       <c r="P66" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q66" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B67" t="s">
-        <v>536</v>
+        <v>557</v>
       </c>
       <c r="C67" t="s">
-        <v>537</v>
+        <v>558</v>
       </c>
       <c r="D67" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E67" t="s">
-        <v>538</v>
+        <v>559</v>
       </c>
       <c r="F67" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G67" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H67" t="s">
-        <v>539</v>
+        <v>560</v>
       </c>
       <c r="I67"/>
       <c r="J67"/>
       <c r="K67"/>
       <c r="L67"/>
       <c r="M67" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N67" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O67" t="s">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="P67" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q67" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B68" t="s">
-        <v>541</v>
+        <v>562</v>
       </c>
       <c r="C68" t="s">
-        <v>542</v>
+        <v>563</v>
       </c>
       <c r="D68" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E68" t="s">
-        <v>538</v>
+        <v>559</v>
       </c>
       <c r="F68" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G68" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H68" t="s">
-        <v>543</v>
+        <v>564</v>
       </c>
       <c r="I68"/>
       <c r="J68"/>
       <c r="K68"/>
       <c r="L68"/>
       <c r="M68" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N68" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O68" t="s">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="P68" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q68" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B69" t="s">
-        <v>544</v>
+        <v>565</v>
       </c>
       <c r="C69" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="D69" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E69" t="s">
-        <v>546</v>
+        <v>567</v>
       </c>
       <c r="F69" t="s">
-        <v>547</v>
+        <v>568</v>
       </c>
       <c r="G69" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H69" t="s">
-        <v>546</v>
+        <v>567</v>
       </c>
       <c r="I69"/>
       <c r="J69"/>
       <c r="K69"/>
       <c r="L69"/>
       <c r="M69" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N69" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O69" t="s">
-        <v>548</v>
+        <v>569</v>
       </c>
       <c r="P69" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q69" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B70" t="s">
-        <v>549</v>
+        <v>570</v>
       </c>
       <c r="C70" t="s">
-        <v>550</v>
+        <v>571</v>
       </c>
       <c r="D70" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E70" t="s">
-        <v>551</v>
+        <v>572</v>
       </c>
       <c r="F70" t="s">
-        <v>547</v>
+        <v>568</v>
       </c>
       <c r="G70" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H70" t="s">
-        <v>551</v>
+        <v>572</v>
       </c>
       <c r="I70"/>
       <c r="J70"/>
       <c r="K70"/>
       <c r="L70"/>
       <c r="M70" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N70" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O70" t="s">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="P70" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q70" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B71" t="s">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="C71" t="s">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c r="D71" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E71" t="s">
-        <v>555</v>
+        <v>576</v>
       </c>
       <c r="F71" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
       <c r="G71" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H71" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="I71"/>
       <c r="J71"/>
       <c r="K71"/>
       <c r="L71"/>
       <c r="M71" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N71" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O71" t="s">
-        <v>548</v>
+        <v>569</v>
       </c>
       <c r="P71" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q71" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B72" t="s">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="C72" t="s">
-        <v>559</v>
+        <v>580</v>
       </c>
       <c r="D72" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E72" t="s">
-        <v>560</v>
+        <v>581</v>
       </c>
       <c r="F72" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
       <c r="G72" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H72" t="s">
-        <v>560</v>
+        <v>581</v>
       </c>
       <c r="I72"/>
       <c r="J72"/>
       <c r="K72"/>
       <c r="L72"/>
       <c r="M72" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N72" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O72" t="s">
-        <v>548</v>
+        <v>569</v>
       </c>
       <c r="P72" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q72" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="B73" t="s">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="C73" t="s">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="D73" t="s">
-        <v>564</v>
+        <v>585</v>
       </c>
       <c r="E73" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="F73" t="s">
-        <v>565</v>
+        <v>586</v>
       </c>
       <c r="G73" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H73" t="s">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="I73"/>
       <c r="J73"/>
       <c r="K73"/>
       <c r="L73"/>
       <c r="M73" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N73" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O73" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="P73" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q73" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="B74" t="s">
-        <v>568</v>
+        <v>589</v>
       </c>
       <c r="C74" t="s">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="D74" t="s">
-        <v>564</v>
+        <v>585</v>
       </c>
       <c r="E74" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="F74" t="s">
-        <v>565</v>
+        <v>586</v>
       </c>
       <c r="G74" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H74" t="s">
-        <v>570</v>
+        <v>591</v>
       </c>
       <c r="I74"/>
       <c r="J74"/>
       <c r="K74"/>
       <c r="L74"/>
       <c r="M74" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N74" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O74" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="P74" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q74" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="B75" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="C75" t="s">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="D75" t="s">
-        <v>564</v>
+        <v>585</v>
       </c>
       <c r="E75" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="F75" t="s">
-        <v>565</v>
+        <v>586</v>
       </c>
       <c r="G75" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H75" t="s">
-        <v>572</v>
+        <v>593</v>
       </c>
       <c r="I75"/>
       <c r="J75"/>
       <c r="K75"/>
       <c r="L75"/>
       <c r="M75" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N75" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O75" t="s">
-        <v>573</v>
+        <v>594</v>
       </c>
       <c r="P75" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q75" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="B76" t="s">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="C76" t="s">
-        <v>576</v>
+        <v>597</v>
       </c>
       <c r="D76" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E76" t="s">
-        <v>577</v>
+        <v>598</v>
       </c>
       <c r="F76" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="G76" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="H76" t="s">
-        <v>580</v>
+        <v>601</v>
       </c>
       <c r="I76"/>
       <c r="J76"/>
       <c r="K76"/>
       <c r="L76"/>
       <c r="M76" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N76" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O76" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="P76" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q76" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="B77" t="s">
-        <v>582</v>
+        <v>603</v>
       </c>
       <c r="C77" t="s">
-        <v>583</v>
+        <v>604</v>
       </c>
       <c r="D77" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E77" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="F77" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="G77" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="H77" t="s">
-        <v>585</v>
+        <v>606</v>
       </c>
       <c r="I77"/>
       <c r="J77"/>
       <c r="K77"/>
       <c r="L77"/>
       <c r="M77" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N77" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O77" t="s">
-        <v>586</v>
+        <v>607</v>
       </c>
       <c r="P77" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q77" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="B78" t="s">
-        <v>587</v>
+        <v>608</v>
       </c>
       <c r="C78" t="s">
-        <v>588</v>
+        <v>609</v>
       </c>
       <c r="D78" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E78" t="s">
-        <v>589</v>
+        <v>610</v>
       </c>
       <c r="F78" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="G78" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="H78" t="s">
-        <v>590</v>
+        <v>611</v>
       </c>
       <c r="I78"/>
       <c r="J78"/>
       <c r="K78"/>
       <c r="L78"/>
       <c r="M78" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N78" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O78" t="s">
-        <v>591</v>
+        <v>612</v>
       </c>
       <c r="P78" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q78" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="B79" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="C79" t="s">
-        <v>592</v>
+        <v>613</v>
       </c>
       <c r="D79" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E79" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="F79" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="G79" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="H79" t="s">
-        <v>593</v>
+        <v>614</v>
       </c>
       <c r="I79"/>
       <c r="J79"/>
       <c r="K79"/>
       <c r="L79"/>
       <c r="M79" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N79" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O79" t="s">
-        <v>591</v>
+        <v>612</v>
       </c>
       <c r="P79" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q79" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="B80" t="s">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="C80" t="s">
-        <v>595</v>
+        <v>616</v>
       </c>
       <c r="D80" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E80" t="s">
-        <v>596</v>
+        <v>617</v>
       </c>
       <c r="F80" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="G80" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="H80" t="s">
-        <v>597</v>
+        <v>618</v>
       </c>
       <c r="I80"/>
       <c r="J80"/>
       <c r="K80"/>
       <c r="L80"/>
       <c r="M80" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N80" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O80" t="s">
-        <v>598</v>
+        <v>619</v>
       </c>
       <c r="P80" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q80" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="B81" t="s">
+        <v>620</v>
+      </c>
+      <c r="C81" t="s">
+        <v>621</v>
+      </c>
+      <c r="D81" t="s">
+        <v>249</v>
+      </c>
+      <c r="E81" t="s">
+        <v>221</v>
+      </c>
+      <c r="F81" t="s">
         <v>599</v>
       </c>
-      <c r="C81" t="s">
+      <c r="G81" t="s">
         <v>600</v>
       </c>
-      <c r="D81" t="s">
-        <v>228</v>
-      </c>
-      <c r="E81" t="s">
-        <v>200</v>
-      </c>
-      <c r="F81" t="s">
-        <v>578</v>
-      </c>
-      <c r="G81" t="s">
-        <v>579</v>
-      </c>
       <c r="H81" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="I81"/>
       <c r="J81"/>
       <c r="K81"/>
       <c r="L81"/>
       <c r="M81" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N81" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O81" t="s">
-        <v>601</v>
+        <v>622</v>
       </c>
       <c r="P81" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q81" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="B82" t="s">
-        <v>602</v>
+        <v>623</v>
       </c>
       <c r="C82" t="s">
-        <v>603</v>
+        <v>624</v>
       </c>
       <c r="D82" t="s">
-        <v>604</v>
+        <v>625</v>
       </c>
       <c r="E82" t="s">
-        <v>605</v>
+        <v>626</v>
       </c>
       <c r="F82" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="G82" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="H82" t="s">
-        <v>606</v>
+        <v>627</v>
       </c>
       <c r="I82"/>
       <c r="J82"/>
       <c r="K82"/>
       <c r="L82"/>
       <c r="M82" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="N82" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="O82" t="s">
-        <v>607</v>
+        <v>628</v>
       </c>
       <c r="P82" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="Q82" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -8414,10 +8749,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>608</v>
+        <v>629</v>
       </c>
       <c r="B1" t="s">
-        <v>609</v>
+        <v>630</v>
       </c>
     </row>
     <row r="2">
@@ -8425,7 +8760,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>610</v>
+        <v>631</v>
       </c>
     </row>
     <row r="3">
@@ -8433,7 +8768,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>611</v>
+        <v>632</v>
       </c>
     </row>
     <row r="4">
@@ -8441,7 +8776,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>612</v>
+        <v>633</v>
       </c>
     </row>
     <row r="5">
@@ -8449,7 +8784,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>613</v>
+        <v>634</v>
       </c>
     </row>
     <row r="6">
@@ -8457,7 +8792,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>614</v>
+        <v>635</v>
       </c>
     </row>
     <row r="7">
@@ -8465,7 +8800,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>615</v>
+        <v>636</v>
       </c>
     </row>
     <row r="8">
@@ -8473,7 +8808,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>616</v>
+        <v>637</v>
       </c>
     </row>
     <row r="9">
@@ -8481,7 +8816,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>617</v>
+        <v>638</v>
       </c>
     </row>
     <row r="10">
@@ -8489,7 +8824,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>618</v>
+        <v>639</v>
       </c>
     </row>
     <row r="11">
@@ -8497,7 +8832,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>619</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>
@@ -8550,13 +8885,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="B1" t="s">
-        <v>621</v>
+        <v>642</v>
       </c>
       <c r="C1" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2">
@@ -8564,10 +8899,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
       <c r="C2" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
     </row>
     <row r="3">
@@ -8575,10 +8910,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>624</v>
+        <v>645</v>
       </c>
       <c r="C3" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
     </row>
     <row r="4">
@@ -8586,10 +8921,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>625</v>
+        <v>646</v>
       </c>
       <c r="C4" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
     </row>
     <row r="5">
@@ -8597,10 +8932,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>626</v>
+        <v>647</v>
       </c>
       <c r="C5" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
     </row>
     <row r="6">
@@ -8608,10 +8943,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="C6" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
     </row>
     <row r="7">
@@ -8619,10 +8954,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>628</v>
+        <v>649</v>
       </c>
       <c r="C7" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8">
@@ -8630,10 +8965,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>629</v>
+        <v>650</v>
       </c>
       <c r="C8" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
     </row>
     <row r="9">
@@ -8641,10 +8976,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>630</v>
+        <v>651</v>
       </c>
       <c r="C9" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
     </row>
     <row r="10">
@@ -8652,10 +8987,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>631</v>
+        <v>652</v>
       </c>
       <c r="C10" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
     </row>
     <row r="11">
@@ -8663,10 +8998,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>632</v>
+        <v>653</v>
       </c>
       <c r="C11" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
     </row>
     <row r="12">
@@ -8674,10 +9009,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>633</v>
+        <v>654</v>
       </c>
       <c r="C12" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
     </row>
     <row r="13">
@@ -8685,10 +9020,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>634</v>
+        <v>655</v>
       </c>
       <c r="C13" t="s">
-        <v>635</v>
+        <v>656</v>
       </c>
     </row>
     <row r="14">
@@ -8696,10 +9031,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>636</v>
+        <v>657</v>
       </c>
       <c r="C14" t="s">
-        <v>635</v>
+        <v>656</v>
       </c>
     </row>
   </sheetData>
